--- a/outputs/01.2026/transaction_ids.xlsx
+++ b/outputs/01.2026/transaction_ids.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clearwateranalytics-my.sharepoint.com/personal/matthewray_clearwateranalytics_com/Documents/Desktop/Ladder/Python/GL_Entries/outputs/01.2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_AA7915F7CF47C263CDDCBD5F1FDEC908E6409431" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC460161-9DA4-4BCC-8CA9-0B258D2F9AD0}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_AA7915F7CF47C263CDDCBD5F1FDEC908E6409431" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FE11122-266F-465D-A796-8FB42DE1BB1B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14565" yWindow="16080" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bulk_upload" sheetId="1" r:id="rId1"/>
     <sheet name="raw" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -487,11 +488,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +505,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -537,18 +546,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -562,6 +574,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4984,6 +5000,69 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011D64AB-CEFA-496D-AED2-F98973EB1970}">
+  <dimension ref="J3:U15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+    </row>
+    <row r="4" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="Q4" s="4">
+        <v>61651120</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.13333300000000001</v>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4">
+        <f>Q4*R4*0.01</f>
+        <v>82201.287829600013</v>
+      </c>
+      <c r="U4" s="4"/>
+    </row>
+    <row r="5" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+    </row>
+    <row r="9" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="Q9">
+        <v>68501.25</v>
+      </c>
+    </row>
+    <row r="10" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="Q10" s="4">
+        <v>82201.287829600013</v>
+      </c>
+    </row>
+    <row r="14" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <v>195413.02</v>
+      </c>
+    </row>
+    <row r="15" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>-161019.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{31b54463-0dc6-4729-9f0b-886b1c3961cf}" enabled="1" method="Standard" siteId="{3dd59dce-9563-4ed5-b9aa-d0320fb1b440}" removed="0"/>
